--- a/hardware/SPI NAND Flash Breakout Board/v0.1.0/spi_nand_bom.xlsx
+++ b/hardware/SPI NAND Flash Breakout Board/v0.1.0/spi_nand_bom.xlsx
@@ -8,13 +8,12 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://emailsc-my.sharepoint.com/personal/dstjohn_email_sc_edu/Documents/Desktop/Edge-Computing-Power-Management-Development-Kit/hardware/SPI NAND Flash Breakout Board/v0.1.0/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="96" documentId="11_5A4B2C90D3AEA2794F446FDFF5D8B87F547F059E" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A4C5BA05-CDF1-4C9C-8854-E9645F8CE9FC}"/>
+  <xr:revisionPtr revIDLastSave="97" documentId="11_5A4B2C90D3AEA2794F446FDFF5D8B87F547F059E" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7011B3E0-24B8-4C40-B0AA-E9A767C77FCB}"/>
   <bookViews>
-    <workbookView xWindow="-105" yWindow="0" windowWidth="14610" windowHeight="17385" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1125" yWindow="1125" windowWidth="21600" windowHeight="12585" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="BOM" sheetId="3" r:id="rId1"/>
-    <sheet name="JLCPCB" sheetId="4" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -34,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="66" uniqueCount="53">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="40">
   <si>
     <t>Notes</t>
   </si>
@@ -84,30 +83,9 @@
     <t>TXB0106PWR</t>
   </si>
   <si>
-    <t xml:space="preserve">Comment </t>
-  </si>
-  <si>
-    <t>Footprint</t>
-  </si>
-  <si>
-    <t>1uF</t>
-  </si>
-  <si>
-    <t>100nF</t>
-  </si>
-  <si>
     <t>Conn_01x08_Pin</t>
   </si>
   <si>
-    <t>10k</t>
-  </si>
-  <si>
-    <t>TXB0106PW</t>
-  </si>
-  <si>
-    <t>AP2127K-1.8</t>
-  </si>
-  <si>
     <t>C1,C2,C5</t>
   </si>
   <si>
@@ -124,24 +102,6 @@
   </si>
   <si>
     <t>U3</t>
-  </si>
-  <si>
-    <t>Capacitor_SMD:C_0805_2012Metric</t>
-  </si>
-  <si>
-    <t>Connector_PinSocket_2.54mm:PinSocket_1x08_P2.54mm_Vertical</t>
-  </si>
-  <si>
-    <t>Resistor_SMD:R_0805_2012Metric</t>
-  </si>
-  <si>
-    <t>Breakout:SON127P600X800X80-8N</t>
-  </si>
-  <si>
-    <t>Package_SO:TSSOP-16_4.4x5mm_P0.65mm</t>
-  </si>
-  <si>
-    <t>Package_TO_SOT_SMD:SOT-23-5</t>
   </si>
   <si>
     <t>1uF (0805_2012)</t>
@@ -202,7 +162,7 @@
   <numFmts count="3">
     <numFmt numFmtId="44" formatCode="_(&quot;$&quot;* #,##0.00_);_(&quot;$&quot;* \(#,##0.00\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
     <numFmt numFmtId="43" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
-    <numFmt numFmtId="166" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="164" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;??_);_(@_)"/>
   </numFmts>
   <fonts count="11">
     <font>
@@ -311,8 +271,8 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="166" fontId="3" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="166" fontId="5" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -550,13 +510,13 @@
     </row>
     <row r="2" spans="1:12">
       <c r="A2" t="s">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="B2" t="s">
-        <v>36</v>
+        <v>23</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>43</v>
+        <v>30</v>
       </c>
       <c r="D2" s="7">
         <v>3</v>
@@ -574,7 +534,7 @@
       </c>
       <c r="H2" s="2"/>
       <c r="I2" s="13" t="s">
-        <v>44</v>
+        <v>31</v>
       </c>
       <c r="J2" t="s">
         <v>14</v>
@@ -582,13 +542,13 @@
     </row>
     <row r="3" spans="1:12">
       <c r="A3" t="s">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="B3" t="s">
-        <v>37</v>
+        <v>24</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>45</v>
+        <v>32</v>
       </c>
       <c r="D3" s="7">
         <v>3</v>
@@ -606,7 +566,7 @@
       </c>
       <c r="H3" s="2"/>
       <c r="I3" s="5" t="s">
-        <v>47</v>
+        <v>34</v>
       </c>
     </row>
     <row r="4" spans="1:12">
@@ -614,7 +574,7 @@
         <v>1</v>
       </c>
       <c r="B4" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="C4" s="2"/>
       <c r="D4" s="7">
@@ -625,25 +585,25 @@
         <v>3</v>
       </c>
       <c r="F4" s="10" t="s">
-        <v>46</v>
+        <v>33</v>
       </c>
       <c r="G4" s="10" t="s">
-        <v>46</v>
+        <v>33</v>
       </c>
       <c r="H4" s="2"/>
       <c r="I4" s="2" t="s">
-        <v>46</v>
+        <v>33</v>
       </c>
     </row>
     <row r="5" spans="1:12">
       <c r="A5" t="s">
-        <v>26</v>
+        <v>19</v>
       </c>
       <c r="B5" t="s">
-        <v>41</v>
+        <v>28</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>48</v>
+        <v>35</v>
       </c>
       <c r="D5" s="7">
         <v>4</v>
@@ -661,15 +621,15 @@
       </c>
       <c r="H5" s="2"/>
       <c r="I5" s="12" t="s">
-        <v>42</v>
+        <v>29</v>
       </c>
     </row>
     <row r="6" spans="1:12">
       <c r="A6" t="s">
-        <v>27</v>
+        <v>20</v>
       </c>
       <c r="B6" t="s">
-        <v>52</v>
+        <v>39</v>
       </c>
       <c r="C6" t="s">
         <v>2</v>
@@ -690,15 +650,15 @@
       </c>
       <c r="H6" s="2"/>
       <c r="I6" s="12" t="s">
-        <v>40</v>
+        <v>27</v>
       </c>
     </row>
     <row r="7" spans="1:12">
       <c r="A7" t="s">
-        <v>28</v>
+        <v>21</v>
       </c>
       <c r="B7" t="s">
-        <v>51</v>
+        <v>38</v>
       </c>
       <c r="C7" t="s">
         <v>15</v>
@@ -718,18 +678,18 @@
         <v>5.4</v>
       </c>
       <c r="I7" s="12" t="s">
-        <v>38</v>
+        <v>25</v>
       </c>
     </row>
     <row r="8" spans="1:12">
       <c r="A8" t="s">
-        <v>29</v>
+        <v>22</v>
       </c>
       <c r="B8" t="s">
-        <v>50</v>
+        <v>37</v>
       </c>
       <c r="C8" t="s">
-        <v>49</v>
+        <v>36</v>
       </c>
       <c r="D8" s="7">
         <v>1</v>
@@ -746,7 +706,7 @@
         <v>0.60000000000000009</v>
       </c>
       <c r="I8" s="12" t="s">
-        <v>39</v>
+        <v>26</v>
       </c>
     </row>
     <row r="9" spans="1:12">
@@ -773,107 +733,4 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId6"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7856D750-8709-4059-BB67-118BDB84F0EC}">
-  <dimension ref="A1:C8"/>
-  <sheetFormatPr defaultRowHeight="14.25"/>
-  <cols>
-    <col min="1" max="1" width="20.125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="11.875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="57.375" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:3" s="6" customFormat="1" ht="15">
-      <c r="A1" s="6" t="s">
-        <v>16</v>
-      </c>
-      <c r="B1" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="C1" s="6" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3">
-      <c r="A2" t="s">
-        <v>18</v>
-      </c>
-      <c r="B2" t="s">
-        <v>24</v>
-      </c>
-      <c r="C2" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3">
-      <c r="A3" t="s">
-        <v>19</v>
-      </c>
-      <c r="B3" t="s">
-        <v>25</v>
-      </c>
-      <c r="C3" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3">
-      <c r="A4" t="s">
-        <v>20</v>
-      </c>
-      <c r="B4" t="s">
-        <v>1</v>
-      </c>
-      <c r="C4" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3">
-      <c r="A5" t="s">
-        <v>21</v>
-      </c>
-      <c r="B5" t="s">
-        <v>26</v>
-      </c>
-      <c r="C5" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3">
-      <c r="A6" t="s">
-        <v>2</v>
-      </c>
-      <c r="B6" t="s">
-        <v>27</v>
-      </c>
-      <c r="C6" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3">
-      <c r="A7" t="s">
-        <v>22</v>
-      </c>
-      <c r="B7" t="s">
-        <v>28</v>
-      </c>
-      <c r="C7" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3">
-      <c r="A8" t="s">
-        <v>23</v>
-      </c>
-      <c r="B8" t="s">
-        <v>29</v>
-      </c>
-      <c r="C8" t="s">
-        <v>35</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
 </file>